--- a/2025zj/2025zj.xlsx
+++ b/2025zj/2025zj.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhong\Documents\2025zhejiang\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhong\Documents\GitHub\site\2025zj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75B48602-1128-4098-98C5-5862B352B590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E397179E-E6DA-451B-A2EB-3FA71E96DEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="0" windowWidth="20235" windowHeight="15030" tabRatio="1000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封面" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="271">
   <si>
     <t>申  报  书</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>申报日期：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         年       月       日</t>
   </si>
   <si>
     <r>
@@ -134,24 +131,12 @@
     <t>与提供的资质证明材料中名称一致</t>
   </si>
   <si>
-    <t>地方国企、民营企业</t>
-  </si>
-  <si>
     <t>引进职务</t>
   </si>
   <si>
     <t>引进地方</t>
   </si>
   <si>
-    <t>省</t>
-  </si>
-  <si>
-    <t>市</t>
-  </si>
-  <si>
-    <t>区/县</t>
-  </si>
-  <si>
     <t>用人单位联系人</t>
   </si>
   <si>
@@ -168,9 +153,6 @@
   </si>
   <si>
     <t>回国（来华）时间</t>
-  </si>
-  <si>
-    <t>尚未回国（来华）填写预估时间</t>
   </si>
   <si>
     <t>是否申报过上一批计划（2024年）</t>
@@ -213,21 +195,12 @@
     <t>申报人技术专长</t>
   </si>
   <si>
-    <t>请用1-3个关键词描述</t>
-  </si>
-  <si>
     <t>申报人基本情况
 （500字以内）</t>
   </si>
   <si>
-    <t>包括申报人重要履历、主要技术能力描述、标志性的成果或荣誉等，陈述请突出重点。</t>
-  </si>
-  <si>
     <t>引进企业基本情况
 （800字以内）</t>
-  </si>
-  <si>
-    <t>包括从事业务领域、核心技术、经营战略、主要客户群、在产业链中的位置和地位等。</t>
   </si>
   <si>
     <t>二、主要学历</t>
@@ -435,63 +408,6 @@
   </si>
   <si>
     <t>申报人拟实现工作目标及可行性论证（限1500字）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t>在匿名评审过程中是否有需要回避的专家和单位，如果有，请详细列出：
-                 □有</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">                            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">       □无</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t>本人承诺以上信息真实、完整、有效，不存在违背科研诚信要求的行为，如有虚假信息愿意承担一切法律责任。入选后全职到岗工作，在国内连续工作不少于三年。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">
-                    申报人签字：                  日期：</t>
-    </r>
   </si>
   <si>
     <t>七、用人单位情况及承诺</t>
@@ -1088,15 +1004,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">样本部署 https://edqaa.com
-12 兆源代码
-1000师生使用
-产生两百兆数据
-运行6个月无故障
-</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>美国国家科学基金</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1113,10 +1020,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">在谷歌云上部署运维 特拉华州立大学中国校区教学过程和质量评估系统，支持常年400学生的全部网络课业，每人每学期平均50个提交记录，一兆数据。这些合作项目每年为特拉华州立大学200多万美元，因为数据支撑高质量，使合作项目年年通过质量评审得以续签，累计创收近亿人民币。  </t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>2001.9-2025.6</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1130,14 +1033,6 @@
   </si>
   <si>
     <t>教学、科研和工具性开源软件 https://zhongyanlin.github.io/site</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是唯一的开发着和维护者</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>本人是 https://edqaa.com 的唯一运维老师，并拥有全部知识产权。同时，承担约75%的教学和质量评估工作（每年约600人课，相当于国内老师的3倍教学量和6倍课业量）。这些工作相当于近千万人民币的收益</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -1202,79 +1097,195 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">三年项目提案：EDQAA 评估平台的全球推广和应用
-一、未来三年工作目标
-1. 研发目标
-优化 EDQAA 的高并发性能，以支持大规模课程（每门课程最多 2,000 名学生）。
-集成 AI 辅助评分和反馈，在不损害学术诚信的前提下进一步减轻教师工作量。
-为不同教育水平（K-12、大学、职业培训）开发可定制的评估模块。
-扩展多语言支持（英语、中文、西班牙语等），以覆盖全球市场。
-二、预期成果
-在 10 多个国家的至少 100 所大学/培训机构实现全球应用。
-建立一个包含 5,000 万份已评分提交材料的数据库，用于纵向教育质量研究。
-与政府教育机构和私人培训机构建立合作伙伴关系。
-通过机构许可和企业级 SaaS 订阅确保收入来源。
-3. 产业化目标
-开发具有可扩展云部署的商业级 SaaS 基础架构。
-在亚洲、北美和欧洲建立区域分销和技术支持中心。
-将 EDQAA 打包为白标产品，面向学习管理系统 (LMS) 提供商和教育科技经销商。
-4. 团队培训
-将研发团队扩充至 15 名以上具备教育人工智能、数据分析和用户体验/用户界面 (UX/UI) 设计专业知识的工程师。
-培训一支专注于教育科技应用和机构推广的销售和营销团队。
-建立由国际教授和教育政策专家组成的学术顾问委员会。
-5. 行业发展目标
-在教育改革政策中推广基于证据的评估方法。
-为全球教师引入数字评估素养培训。
-鼓励人工智能教学工具与强大的评估系统进行全行业整合。
-6. 社会效益
-通过确保学生的持续参与来提高全球教育质量。
-通过提供价格合理的先进评估工具来减少教育不平等。
-提供实时学习分析，帮助学习困难的学生避免失败。
-二、目标设定依据
-背景
-数字教育革命使学习内容丰富多彩，但学生参与度和评估质量却落后。
-在包括中国在内的许多国家，一些大学课程缺乏一致的评估——没有测验、项目或主动学习要求。
-如果没有有效的评估，学生就会分心，注意力会分散，容易被各种干扰因素（例如课堂上的抖音）所干扰。
-EDQAA 通过自动化评分、跟踪参与度和大规模分析学习成果来解决这个问题。
-意义和重要性
-支持从以教学为中心到以学习为中心的教育转型。
-实现数据驱动的教学质量保证，与现代教育改革议程相一致。
-为无法聘请大型评分团队的机构提供经济高效、可扩展的解决方案。
-三、待解决的关键技术问题
-可扩展性
-当前容量：每门课程 600 名学生，每名学生提交 55 篇以上作业。
-目标：每门课程 2,000 名以上学生，100,000 个并发用户。
-技术参数：峰值负载下页面加载时间小于 2 秒。
-AI 集成评分
-自动识别并评分结构化答案、论文和项目报告。
-针对学术诚信和抄袭检测进行微调的 AI 模型。
-多语言支持
-界面和题库的高精度翻译和本地化。
-数据分析
-实时仪表盘显示学习趋势、学生风险警报和教学效果评分。
-与现有学习管理系统 (LMS) 集成
-用于与 Moodle、Blackboard、Canvas 和政府电子学习平台互操作的 API。
-四、创新点
-国内外对比分析
-国外学习管理系统 (LMS) 平台（例如 Canvas、Blackboard）具备评估功能，但缺乏像 EDQAA 那样极高的评分效率和高提交频率支持。
-中国国内平台通常专注于直播和作业上传，但缺乏详细的多层次分析或 AI 辅助评分。
-EDQAA 的核心优势：
-处理每名学生每门课程的大量提交。
-自动生成学习质量指标。
-注重频繁、持续的评估，而非期末评分。
-关键技术亟待开发
-AI 驱动的自动化评分系统，将评分成本/时间降低 80% 以上。
-安全、可扩展的云架构，可用于国家级部署。
-强大的学术不端行为检测算法，有效防止 AI 时代的作弊行为。
-五、可行性研究分析
-技术可行性
-该平台已上线 (https://edqaa.com)，并已验证可处理大型课程。
-部署于 Google Cloud，可通过 Kubernetes 和负载均衡进行扩展。
-核心评分、分析和报告系统已稳定运行。
-市场可行性
-在线和混合式学习在全球范围内快速扩张。
-教育改革对循证质量评估工具的需求日益增长                       </t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <t>Lin Zhongyan (林中焰)</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>天宸启桦数字科技有限公司</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省宁波市</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年8月10日</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>地方民营</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁波市</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>奉化区</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年11月（计划）</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>数字教育</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国高教协会认证数字化
+教学专家</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>数字教育技术,信息系统工程,教育人工智能</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能高效专业教学，用大数据的教学质量评估，教育市场开发</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级科学家</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>1393306978@qq.com</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴爱英</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">样本部署 https://edqaa.com
+12 兆源代码
+1000师生使用
+产生两百兆数据年
+运行6个月无故障
+</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>本人是 https://edqaa.com 的唯一运维老师，并拥有全部知识产权。同时，承担约75%的教学和质量评估工作（每年约600人课，相当于国内老师的3倍教学量和6倍课业量）。这些工作相当于近300万美元的收益</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是唯一的开发着和维护者
+约 2mb源代码</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">在谷歌云上部署运维 特拉华州立大学中国校区教学过程和质量评估系统，支持常年400学生的全部网络课业，每人每学期平均50个提交记录，一兆数据。这些合作项目每年为特拉华州立大学300多万美元，因为数据支撑高质量，使合作项目年年通过质量评审得以续签，累计创收近8000万人民币。  </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">大数据教学、学习与评估管理平台的功能TeaLeaMan加强和全球营销的三年工作计划
+一、背景与理念
+过去十年，数字教育飞速发展。多媒体内容、在线讲座和开放教育资源使得高质量的学习资料比以往任何时候都更容易获取。如今，生成式人工智能使学生能够即时完成作业、论文和习题集。虽然这些发展丰富了教学资源，但也暴露出一个关键的弱点：如果没有认真、结构化和频繁的评估，许多学生实际上并没有学习——无论课程准备得多么充分。
+在全球许多课堂中，缺乏一致且有数据支持的评估意味着学生可能被动地听课、一边看娱乐视频一边学习，或者完全不参与学习。等到期末考试来临时，为时已晚，无法扭转学习的损失，导致高挂失率和教育机会的浪费。
+TeaLeaMan 通过提供一个可扩展的、大数据驱动的评估管理平台，直接应对了这一挑战。该系统基于我个人的教学需求构建，它是我能每学期教近300个学生注册，涵盖6个班，每位学生平均提交55份实际作业（包括测验、阅读材料、作业、项目和考试）。这为课程质量评估和学习分析提供了丰富的数据来源。该系统与HuggingFace和ChatGPT等模型的集成，使大部分评分工作自动化，从而实现了较高的提交频率，同时又不会给老师带来负担。
+其理念简单却至关重要：频繁、可追踪且有意义的评估能够保持学生的参与度和责任感。了解成绩持续更新且有不及格风险的学生会投入更多时间和精力学习——这是即使是最好的课堂教学也无法保证的。
+宁波作为新一线城市，高新智能产业领先，亟需提升高等教育质量以匹配城市发展新阶段。宁波天宸启桦数字科技公司一直从事数字教育相关产业，也有意进入高等教育技术领域。把TeaLeaMan 这个比较成熟的平台和天宸启桦的产品相结合，强强联合，一定能在宁波推广基于AI与大数据的智能化教学质量控制体系，助力宁波高等教育质量在短期内实现显著跃升，为城市创新发展提供强有力的人才与智力支撑。
+二、未来三年的目标
+1. 研发与产品改进
+a)	优化性能，以应对10万并发用户，页面加载时间低于2秒。
+b)	完善 AI 辅助的论文、项目和结构化答案评分系统，并进行抄袭和 AI 生成内容检测。
+c)	为 K-12、高等教育和职业培训开发可定制的评估模板。
+d)	扩展多语言支持（英语、中文、日语、法语、西班牙语）。
+e)	构建 API，实现与主流 LMS 平台（Moodle、Blackboard、Canvas）的无缝集成。
+2. 市场拓展
+a)	在宁波高校和培训机构开展推广活动，并逐步拓展至国内和国际市场。
+b)	将 TeaLeaMan 打包成多种交付模式：SaaS 订阅、白标解决方案和本地安装。
+c)	与政府教育部门、教育科技经销商和私人培训机构建立合作伙伴关系。
+3. 团队和生态系统发展
+a)	将研发团队扩展至 10 名以上精通 AI、数据分析和 UX/UI 设计的工程师。
+b)	建立一个由教授和教育政策专家组成的全球学术顾问委员会。
+c)	培训一支专注于机构教育技术应用的营销和销售团队。
+三、预期成果
+a)	给天宸启桦现有教育技术产品尽可能加入大数据收集和教育质量评估功能
+b)	建立一个包含 5000 万份已评分提交材料的全球数据库，以支持大规模的教育质量纵向研究。
+c)	产生持续的机构许可收入和企业级 SaaS 订阅。
+d)	通过展示持续的、基于证据的评估的益处来影响教育改革。
+e)	通过使先进的评估技术价格合理且易于获取，提高全球教育质量并减少不平等。
+四、可行性分析
+1. 技术可行性： TeaLeaMan 已在 https://edqaa.com 上投入运营，并成功支持了高容量教学。其架构部署在 Google Cloud 上，通过 Kubernetes 管理容器化服务，并实现负载平衡以实现可扩展性。AI 辅助评分模块功能齐全，并且与 HuggingFace 和 ChatGPT 的集成已被证明是可靠的。该系统采用模块化设计，可轻松扩展以支持更多语言以及与其他 LMS 平台的集成点。
+2. 市场可行性：预计全球教育科技市场将快速增长，这得益于在线学习的普及、混合学习模式以及人工智能的融合。然而，大多数学习管理系统 (LMS) 平台仍然侧重于内容交付而非评估。TeaLeaMan 填补了这一市场空白，它采用教师设计的评估优先方法，无需庞大的评分团队即可实现频繁且可扩展的评估。
+五． 结论 在中国，与许多国家一样，由于助教短缺和缺乏高效的评分工具，导致整个学期的学生评估数量极少。TeaLeaMan 提供了一种实用且经过验证的解决方案，对寻求显著提升学习                </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">在匿名评审过程中是否有需要回避的专家和单位，如果有，请详细列出：
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">       无</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>本人承诺以上信息真实、完整、有效，不存在违背科研诚信要求的行为，如有虚假信息愿意承担一切法律责任。入选后全职到岗工作，在国内连续工作不少于三年。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">
+                    申报人签字：                  日期：08/12/2025</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>启明计划</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>林中焰博士，不到16岁时以江西省修水县理科高考总分第一名考入四川大学数学系，后于湖南大学获硕士学位并留校任教。1993年获美国特拉华大学全额奖学金资助，于1997年、1998年分获计算机科学硕士及数学博士学位。早期研究聚焦数学物理方程可解性的数值模拟及其在海洋声学与弹性力学中的应用，成果发表于多篇学术论文，包括在著名的SIAM Appl. Math.的30页长文。
+博士毕业后，曾任职霍尼韦尔公司研发工程师。1999年重返学术界，全职任教于特拉华州立大学计算机与信息科学系。凭借杰出专业能力，于2004 获得终身教职（教学岗）。执教期间，系统讲授计算机及数学专业本硕课程25门，获美国高等教育协会教学认证。
+教学技术创新成就卓著：独立设计并开发了功能完备的基于Web的教学过程管理与质量评估系统（部署于古歌云上https://edqaa.com）。该系统采用全栈现代网络技术，源代码规模达12MB，已成功应用于特拉华州立大学中国校区的教学管理与质量保障。
+积极推动中美教育合作：近年来深度参与中国教育市场开拓，助力建立多个中美合作办学项目，并承担计算机专业核心教学任务。年授课量覆盖约600名学生注册（相当于国内原工作量的三倍），通过其系统高效管理，每课人均提交课业55项，年生成教学评估数据超200MB。其高效教学与基于大数据的质量管理体系连续三年通过严格评估，保障了合作项目的成功续签，累计为合作方创造经济效益约8000万元人民币，对应每年教学工作量贡献收益近300万美元。
+展望与宁波发展契合点：宁波作为新一线城市，高新智能产业领先，亟需提升高等教育质量以匹配城市发展新阶段。在生成式AI时代，教学资源易得，但教学质量保障面临新挑战（如受AI与网络娱乐冲击）。林博士希冀依托数十年教学经验与自主研发的成熟技术，整合进天宸启桦数字科技公司的强大平台，在宁波推广基于AI与大数据的智能化教学质量控制体系，助力宁波高等教育质量在短期内实现显著跃升，为城市创新发展提供强有力的人才与智力支撑。</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>天宸启桦公司成立于2019年，注册资金6000万元，拥有国内领先首创的XR+AI应用技术开发、动画内容设计制作和多媒体互动技术，主要研发利用物联网传感器实现基于AI算法的虚实实时交互的空间影像互动产品。公司旨在打造具有自主知识产权的高品质创新文化IP，拥有以XR技术为核心的全链条团队，能够提供从策划到研发、从技术到生产的一体化服务。公司力求将数字和产业融合，赋能行业实现数字产业化、产业数字化和数字化治理。通过虚拟现实、增强现实、人工智能、区块链、数字教育、数字文旅、数字孪生、游戏社交、商业消费等多种形式的线上线下体验产品，适用于文旅、学校、儿童友好、城市更新、乡村振兴、展览展 示、夜游消费等服务要求。曾承办和协办多起文旅推介和招商活动，荣获“创新先锋、新锐势力”双料大奖、小而美企业、国家高新技术企业等多项荣誉。为拓展产品类型与层次，公司将目光转向教育空间，以人体动态捕捉、实时手势感应、语音交互、数字光影展示、多屏融合等技术打造专属于儿童的沉浸式超媒体空间，赋能幼儿园、早教中心、社区等机构。技术是基底，内容才是核心。开发了安全、艺术、生态、科技、人文等九类主题1000多节课程的海量内容，真正打造了寓教于乐、虚实结合的儿童世界。目前，该项技术已应用到多家幼儿园和教学机构。2023年，广西首个省级超写实文旅数字推广大使数字人正式亮相，通过数字IP、数字导游、数字直播、数字展演等方式为游客提供向导服务，这也是公司在数字人领域的一大尝试。除了文旅产业，基于数据、算力和算法打造的数字人还可以运用在酒店、金融、医疗等场景，为消费者提供可靠、优质、便利的服务。公司正在谋划乡镇元宇宙项目，计划利用建筑、山体、树木、水系等载体，打造一个集灯光秀演、声光互动、虚实结合、亲子互动于一体的元宇宙场馆，包含科探馆、酒店、文旅接待中心等。</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1282,10 +1293,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="yyyymm"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="yyyymm"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,6 +1428,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1621,7 +1640,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1640,7 +1659,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1663,7 +1682,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1674,7 +1693,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1701,7 +1720,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1749,6 +1768,81 @@
       <alignment horizontal="distributed"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1756,127 +1850,116 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1886,9 +1969,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1900,67 +1996,67 @@
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1970,94 +2066,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2067,6 +2118,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2076,6 +2195,116 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>952501</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>130273</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D444BBB-2930-CE86-BD1E-170334C77045}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6324601" y="361951"/>
+          <a:ext cx="952500" cy="1158972"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>116416</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>666750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>446699</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>23716</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DF63398-678C-24BF-B6F8-26A5C15EF472}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2180166" y="5408083"/>
+          <a:ext cx="1706116" cy="648133"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2345,407 +2574,408 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="45"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="A1" s="54"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="45"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="47"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="45"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="45"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
     </row>
     <row r="10" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="45"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="45"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="45"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
+      <c r="A15" s="54"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
+      <c r="A16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="45"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
+      <c r="A18" s="54"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="45"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="45"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="45"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
+      <c r="C21" s="127" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
       <c r="H21" s="38" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="45"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="45"/>
+      <c r="A23" s="54"/>
       <c r="B23" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="C23" s="128" t="s">
+        <v>245</v>
+      </c>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
     </row>
     <row r="24" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="45"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="45"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
+      <c r="C25" s="129" t="s">
+        <v>246</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
     </row>
     <row r="26" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
+      <c r="A26" s="54"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="130" t="s">
+        <v>247</v>
+      </c>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
+      <c r="A29" s="54"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="45"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
+      <c r="A32" s="54"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="45"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="45"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
+      <c r="A34" s="54"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="45"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
+      <c r="A35" s="54"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="45"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
+      <c r="A36" s="54"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
+      <c r="A37" s="54"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="45"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="45"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
+      <c r="A39" s="54"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="45"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
+      <c r="A40" s="54"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="45"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="45"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:G5"/>
-    <mergeCell ref="A6:G7"/>
-    <mergeCell ref="A8:G9"/>
-    <mergeCell ref="A11:G20"/>
-    <mergeCell ref="C25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="A21:A27"/>
@@ -2755,6 +2985,11 @@
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A1:G5"/>
+    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="A8:G9"/>
+    <mergeCell ref="A11:G20"/>
+    <mergeCell ref="C25:G25"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
@@ -2777,14 +3012,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
@@ -2796,301 +3031,317 @@
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="91" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="80" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="105" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="60" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="105" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="55"/>
+        <v>10</v>
+      </c>
+      <c r="B4" s="91" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="89"/>
     </row>
     <row r="5" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="91" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="82"/>
+      <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="105" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="55"/>
+      <c r="E5" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="F5" s="89"/>
     </row>
     <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="65"/>
+      <c r="D6" s="86" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="87"/>
+      <c r="F6" s="34" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" s="107" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="108" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="53"/>
-      <c r="F6" s="34" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="107" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="108" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="53"/>
+        <v>15</v>
+      </c>
+      <c r="B7" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="66"/>
+      <c r="D7" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="87"/>
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
+        <v>16</v>
+      </c>
+      <c r="B8" s="88" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="66"/>
+      <c r="D9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="107" t="s">
-        <v>165</v>
-      </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="56">
+      <c r="E9" s="77">
         <v>546353345</v>
       </c>
-      <c r="F9" s="57"/>
+      <c r="F9" s="78"/>
     </row>
     <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="82"/>
+      <c r="D10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="110" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="56">
+      <c r="E10" s="77">
         <v>3027728304</v>
       </c>
-      <c r="F10" s="57"/>
+      <c r="F10" s="78"/>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="83">
+        <v>36373</v>
+      </c>
+      <c r="C11" s="84"/>
+      <c r="D11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="58">
-        <v>1999</v>
-      </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="111" t="s">
-        <v>167</v>
-      </c>
-      <c r="F11" s="57"/>
+      <c r="E11" s="85" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="78"/>
     </row>
     <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="107" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12" s="54"/>
+        <v>23</v>
+      </c>
+      <c r="B12" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="79" t="s">
+        <v>157</v>
+      </c>
+      <c r="F12" s="66"/>
     </row>
     <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="107" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="54"/>
+        <v>24</v>
+      </c>
+      <c r="B13" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="66"/>
     </row>
     <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="107" t="s">
-        <v>170</v>
-      </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="107" t="s">
-        <v>171</v>
-      </c>
-      <c r="F14" s="54"/>
+        <v>25</v>
+      </c>
+      <c r="B14" s="79" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="65"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="66"/>
     </row>
     <row r="15" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
     </row>
     <row r="16" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="54"/>
+        <v>24</v>
+      </c>
+      <c r="B16" s="79" t="s">
+        <v>248</v>
+      </c>
+      <c r="C16" s="66"/>
       <c r="D16" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="54"/>
+        <v>28</v>
+      </c>
+      <c r="E16" s="79" t="s">
+        <v>258</v>
+      </c>
+      <c r="F16" s="66"/>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="54"/>
+        <v>29</v>
+      </c>
+      <c r="B17" s="79" t="s">
+        <v>249</v>
+      </c>
+      <c r="C17" s="66"/>
+      <c r="D17" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="E17" s="79" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" s="66"/>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="71"/>
+      <c r="A18" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="136" t="s">
+        <v>260</v>
+      </c>
       <c r="C18" s="72"/>
       <c r="D18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="57"/>
+        <v>31</v>
+      </c>
+      <c r="E18" s="77">
+        <v>17857322272</v>
+      </c>
+      <c r="F18" s="78"/>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="70"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="56"/>
-      <c r="F19" s="57"/>
+        <v>32</v>
+      </c>
+      <c r="E19" s="135" t="s">
+        <v>259</v>
+      </c>
+      <c r="F19" s="78"/>
     </row>
     <row r="20" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="62"/>
+        <v>33</v>
+      </c>
+      <c r="B20" s="131" t="s">
+        <v>252</v>
+      </c>
+      <c r="C20" s="76"/>
       <c r="D20" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="62"/>
+        <v>35</v>
+      </c>
+      <c r="E20" s="131" t="s">
+        <v>253</v>
+      </c>
+      <c r="F20" s="76"/>
     </row>
     <row r="21" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="62"/>
+        <v>36</v>
+      </c>
+      <c r="B21" s="131" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" s="76"/>
       <c r="D21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
+        <v>37</v>
+      </c>
+      <c r="E21" s="131" t="s">
+        <v>268</v>
+      </c>
+      <c r="F21" s="76"/>
     </row>
     <row r="22" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="76"/>
+      <c r="D22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="61"/>
-      <c r="F22" s="62"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="76"/>
     </row>
     <row r="23" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
+        <v>40</v>
+      </c>
+      <c r="B23" s="132" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="76"/>
       <c r="D23" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="61"/>
-      <c r="F23" s="62"/>
+        <v>41</v>
+      </c>
+      <c r="E23" s="131" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="76"/>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="63"/>
+        <v>42</v>
+      </c>
+      <c r="B24" s="133" t="s">
+        <v>256</v>
+      </c>
       <c r="C24" s="63"/>
       <c r="D24" s="63"/>
       <c r="E24" s="63"/>
@@ -3098,42 +3349,72 @@
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="54"/>
+        <v>43</v>
+      </c>
+      <c r="B25" s="79" t="s">
+        <v>257</v>
+      </c>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="66"/>
     </row>
     <row r="26" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="66"/>
+        <v>44</v>
+      </c>
+      <c r="B26" s="134" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="68"/>
     </row>
     <row r="27" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
+        <v>45</v>
+      </c>
+      <c r="B27" s="137" t="s">
+        <v>270</v>
+      </c>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
@@ -3146,36 +3427,6 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F3:F5"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="1">
@@ -3183,9 +3434,11 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="B10" r:id="rId1" xr:uid="{55B51698-4ACD-453F-9476-2EF1B9A2367D}"/>
+    <hyperlink ref="E19" r:id="rId2" xr:uid="{129A66D1-034B-479D-A1F3-D50A25013D68}"/>
   </hyperlinks>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -3204,16 +3457,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="75" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
@@ -3226,7 +3479,7 @@
     </row>
     <row r="3" spans="1:8" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -3237,7 +3490,7 @@
     </row>
     <row r="4" spans="1:8" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
@@ -3248,28 +3501,28 @@
     </row>
     <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3277,40 +3530,40 @@
       <c r="B6" s="7"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>1</v>
       </c>
-      <c r="B7" s="112" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="113" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" s="113" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="113" t="s">
-        <v>176</v>
-      </c>
-      <c r="G7" s="113" t="s">
-        <v>177</v>
+      <c r="B7" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>166</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -3318,23 +3571,23 @@
       <c r="A8" s="7">
         <v>2</v>
       </c>
-      <c r="B8" s="112" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="113" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="113" t="s">
-        <v>180</v>
-      </c>
-      <c r="F8" s="113" t="s">
-        <v>181</v>
-      </c>
-      <c r="G8" s="113" t="s">
-        <v>182</v>
+      <c r="B8" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>171</v>
       </c>
       <c r="H8" s="4"/>
     </row>
@@ -3342,50 +3595,50 @@
       <c r="A9" s="7">
         <v>3</v>
       </c>
-      <c r="B9" s="112" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="113" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="113" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="113" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="113" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="113" t="s">
-        <v>187</v>
-      </c>
-      <c r="H9" s="114" t="s">
-        <v>190</v>
+      <c r="B9" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
-      <c r="B10" s="112" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="113" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="113" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" s="113" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" s="113" t="s">
-        <v>189</v>
-      </c>
-      <c r="G10" s="113" t="s">
-        <v>187</v>
-      </c>
-      <c r="H10" s="114" t="s">
-        <v>190</v>
+      <c r="B10" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3400,7 +3653,7 @@
     </row>
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -3412,7 +3665,7 @@
     </row>
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="28" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
@@ -3424,25 +3677,25 @@
     </row>
     <row r="15" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3450,20 +3703,20 @@
       <c r="B16" s="7"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
-      <c r="B17" s="112" t="s">
-        <v>177</v>
+      <c r="B17" s="40" t="s">
+        <v>166</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -3527,13 +3780,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
@@ -3544,7 +3797,7 @@
     </row>
     <row r="3" spans="1:7" s="27" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3553,25 +3806,25 @@
     </row>
     <row r="4" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3579,195 +3832,195 @@
       <c r="B5" s="7"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="29" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
-      <c r="B6" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="D6" s="113" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" s="113" t="s">
-        <v>190</v>
-      </c>
-      <c r="F6" s="114" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="115" t="s">
-        <v>209</v>
+      <c r="B6" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="B7" s="112" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="113" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="113" t="s">
-        <v>195</v>
-      </c>
-      <c r="F7" s="114" t="s">
-        <v>196</v>
-      </c>
-      <c r="G7" s="114" t="s">
-        <v>210</v>
+      <c r="B7" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
-      <c r="B8" s="112" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="113" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="113" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" s="113" t="s">
+      <c r="B8" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8" s="42" t="s">
         <v>199</v>
-      </c>
-      <c r="F8" s="115" t="s">
-        <v>200</v>
-      </c>
-      <c r="G8" s="114" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="B9" s="112" t="s">
+      <c r="B9" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="114" x14ac:dyDescent="0.2">
+      <c r="B10" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" s="49" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+      <c r="B11" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="G11" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="C9" s="113" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="116" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="G12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B13" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" t="s">
         <v>203</v>
       </c>
-      <c r="E9" s="116" t="s">
-        <v>202</v>
-      </c>
-      <c r="F9" s="115" t="s">
-        <v>208</v>
-      </c>
-      <c r="G9" s="114" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="114" x14ac:dyDescent="0.2">
-      <c r="B10" s="117" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="118" t="s">
-        <v>205</v>
-      </c>
-      <c r="E10" s="119" t="s">
-        <v>206</v>
-      </c>
-      <c r="F10" s="118" t="s">
-        <v>207</v>
-      </c>
-      <c r="G10" s="121" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="57" x14ac:dyDescent="0.2">
-      <c r="B11" s="117" t="s">
+      <c r="F13" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="G13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B14" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F14" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="120" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" s="122" t="s">
-        <v>213</v>
-      </c>
-      <c r="E11" s="116" t="s">
-        <v>219</v>
-      </c>
-      <c r="F11" s="118" t="s">
-        <v>215</v>
-      </c>
-      <c r="G11" s="121" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B12" s="116" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="D12" s="122" t="s">
-        <v>218</v>
-      </c>
-      <c r="E12" s="122" t="s">
-        <v>219</v>
-      </c>
-      <c r="F12" s="118" t="s">
-        <v>220</v>
-      </c>
-      <c r="G12" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B13" s="123" t="s">
-        <v>222</v>
-      </c>
-      <c r="C13" s="120" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="122" t="s">
-        <v>223</v>
-      </c>
-      <c r="E13" t="s">
-        <v>214</v>
-      </c>
-      <c r="F13" s="118" t="s">
-        <v>224</v>
-      </c>
-      <c r="G13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="123" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="120" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="118" t="s">
-        <v>226</v>
-      </c>
-      <c r="E14" t="s">
-        <v>214</v>
-      </c>
-      <c r="F14" s="124" t="s">
-        <v>227</v>
-      </c>
       <c r="G14" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3799,15 +4052,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
@@ -3820,130 +4073,130 @@
     </row>
     <row r="3" spans="1:7" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25"/>
-      <c r="B4" s="125" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" s="125" t="s">
-        <v>229</v>
-      </c>
-      <c r="D4" s="113" t="s">
-        <v>244</v>
-      </c>
-      <c r="E4" s="113" t="s">
-        <v>230</v>
-      </c>
-      <c r="F4" s="126" t="s">
-        <v>231</v>
-      </c>
-      <c r="G4" s="126" t="s">
-        <v>238</v>
+      <c r="B4" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="25"/>
-      <c r="B5" s="125" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="125" t="s">
-        <v>233</v>
-      </c>
-      <c r="D5" s="113" t="s">
-        <v>234</v>
-      </c>
-      <c r="E5" s="113" t="s">
-        <v>235</v>
-      </c>
-      <c r="F5" s="126" t="s">
-        <v>236</v>
-      </c>
-      <c r="G5" s="126" t="s">
-        <v>237</v>
+      <c r="B5" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="25"/>
-      <c r="B6" s="125" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" s="125" t="s">
-        <v>239</v>
-      </c>
-      <c r="D6" s="113" t="s">
-        <v>241</v>
-      </c>
-      <c r="E6" s="113" t="s">
-        <v>235</v>
-      </c>
-      <c r="F6" s="126" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="126" t="s">
-        <v>243</v>
+      <c r="B6" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="25"/>
-      <c r="B7" s="125" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>246</v>
-      </c>
-      <c r="D7" s="113" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" s="113" t="s">
+      <c r="B7" s="52" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="F7" s="126" t="s">
-        <v>248</v>
-      </c>
-      <c r="G7" s="126" t="s">
-        <v>254</v>
+      <c r="E7" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="G7" s="53" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="25"/>
-      <c r="B8" s="125" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="125" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="113" t="s">
-        <v>251</v>
-      </c>
-      <c r="E8" s="113" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="126" t="s">
-        <v>252</v>
-      </c>
-      <c r="G8" s="126" t="s">
-        <v>253</v>
+      <c r="B8" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -4004,15 +4257,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="23"/>
@@ -4024,31 +4277,31 @@
       <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
+      <c r="A3" s="94" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
     </row>
     <row r="4" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="127" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
+        <v>77</v>
+      </c>
+      <c r="B4" s="97" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
     </row>
     <row r="5" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="128" t="s">
-        <v>257</v>
+        <v>77</v>
+      </c>
+      <c r="B5" s="98" t="s">
+        <v>242</v>
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="63"/>
@@ -4056,7 +4309,7 @@
     </row>
     <row r="6" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B6" s="63"/>
       <c r="C6" s="63"/>
@@ -4065,18 +4318,18 @@
     </row>
     <row r="7" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="129" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
+        <v>78</v>
+      </c>
+      <c r="B7" s="96" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B8" s="63"/>
       <c r="C8" s="63"/>
@@ -4085,7 +4338,7 @@
     </row>
     <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B9" s="63"/>
       <c r="C9" s="63"/>
@@ -4094,18 +4347,18 @@
     </row>
     <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="129" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
+        <v>79</v>
+      </c>
+      <c r="B10" s="96" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
     </row>
     <row r="11" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B11" s="63"/>
       <c r="C11" s="63"/>
@@ -4114,7 +4367,7 @@
     </row>
     <row r="12" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B12" s="63"/>
       <c r="C12" s="63"/>
@@ -4123,18 +4376,18 @@
     </row>
     <row r="13" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
+        <v>80</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
     </row>
     <row r="14" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B14" s="63"/>
       <c r="C14" s="63"/>
@@ -4143,7 +4396,7 @@
     </row>
     <row r="15" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B15" s="63"/>
       <c r="C15" s="63"/>
@@ -4152,7 +4405,7 @@
     </row>
     <row r="16" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B16" s="63"/>
       <c r="C16" s="63"/>
@@ -4160,29 +4413,29 @@
       <c r="E16" s="63"/>
     </row>
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="76" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
+      <c r="A17" s="94" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
     </row>
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -4256,29 +4509,29 @@
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="76" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="76"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
+      <c r="A29" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="94"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
     </row>
     <row r="30" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -4346,6 +4599,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="B12:E12"/>
@@ -4353,16 +4616,6 @@
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
@@ -4379,16 +4632,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
@@ -4401,52 +4654,52 @@
       <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
+      <c r="A3" s="99" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:8" ht="254.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="130" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
+      <c r="A4" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
     </row>
     <row r="5" spans="1:8" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="80" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
+      <c r="A5" s="138" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
     </row>
     <row r="6" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="81" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
+      <c r="A6" s="139" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4462,6 +4715,7 @@
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4478,26 +4732,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="A1" s="90" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="82"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="63" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B3" s="63"/>
       <c r="C3" s="63"/>
@@ -4506,178 +4760,178 @@
       <c r="F3" s="63"/>
     </row>
     <row r="4" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="71"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="71"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="71" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="71" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="71"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="114" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="115"/>
+      <c r="F6" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="113" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="71"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="66"/>
+    </row>
+    <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="71"/>
+      <c r="C8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="71"/>
+      <c r="F8" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="71"/>
+      <c r="C9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="71"/>
+      <c r="F9" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="70" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="70" t="s">
+      <c r="B10" s="71"/>
+      <c r="C10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="70" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="70" t="s">
+      <c r="E10" s="71"/>
+      <c r="F10" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="119" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="70" t="s">
+      <c r="B11" s="120"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="83" t="s">
+      <c r="E11" s="120"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="121" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="84"/>
-      <c r="F6" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="85" t="s">
+      <c r="B12" s="122"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="121" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="54"/>
-    </row>
-    <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="70" t="s">
+      <c r="E12" s="122"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="113" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="70" t="s">
+      <c r="B13" s="71"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="113" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="70" t="s">
+      <c r="E13" s="71"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="70" t="s">
+      <c r="B14" s="71"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="11" t="s">
+      <c r="E14" s="71"/>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="113" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="70" t="s">
+      <c r="B15" s="71"/>
+      <c r="C15" s="63" t="s">
         <v>121</v>
-      </c>
-      <c r="B10" s="70"/>
-      <c r="C10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="70" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="86" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="86" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" s="87"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="88" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="89"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="88" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="85" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="70"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="85" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="70"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="85" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="70"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="70" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="70"/>
-      <c r="F14" s="16"/>
-    </row>
-    <row r="15" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="85" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="63" t="s">
-        <v>132</v>
       </c>
       <c r="D15" s="63"/>
       <c r="E15" s="63"/>
       <c r="F15" s="63"/>
     </row>
     <row r="16" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="84"/>
-      <c r="C16" s="90" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="92"/>
+      <c r="A16" s="114" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="115"/>
+      <c r="C16" s="116" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="118"/>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="63" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B17" s="63"/>
       <c r="C17" s="63"/>
@@ -4687,61 +4941,61 @@
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B18" s="76" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
+        <v>125</v>
+      </c>
+      <c r="B18" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
       <c r="F18" s="17" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="18"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="95"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="110"/>
       <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="18"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="95"/>
+      <c r="B20" s="108"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="109"/>
+      <c r="E20" s="110"/>
       <c r="F20" s="18"/>
     </row>
     <row r="21" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="18"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="94"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="95"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="110"/>
       <c r="F21" s="18"/>
     </row>
     <row r="22" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="18"/>
-      <c r="B22" s="93"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="95"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="110"/>
       <c r="F22" s="18"/>
     </row>
     <row r="23" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="18"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="95"/>
+      <c r="B23" s="108"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="110"/>
       <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="63" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B24" s="63"/>
       <c r="C24" s="63"/>
@@ -4751,85 +5005,85 @@
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D25" s="96" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="97"/>
+        <v>131</v>
+      </c>
+      <c r="D25" s="111" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" s="112"/>
       <c r="F25" s="20" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" s="62"/>
+      <c r="D26" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="76"/>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" s="62"/>
+      <c r="D27" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="76"/>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" s="62"/>
+      <c r="D28" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="76"/>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E29" s="62"/>
+      <c r="D29" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="76"/>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="21"/>
       <c r="B30" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C30" s="4"/>
-      <c r="D30" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E30" s="62"/>
+      <c r="D30" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="76"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="63" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B31" s="63"/>
       <c r="C31" s="63"/>
@@ -4838,27 +5092,66 @@
       <c r="F31" s="63"/>
     </row>
     <row r="32" spans="1:6" ht="86.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="98" t="s">
-        <v>148</v>
-      </c>
-      <c r="B32" s="99"/>
-      <c r="C32" s="99"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="100"/>
+      <c r="A32" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="106"/>
     </row>
     <row r="33" spans="1:6" ht="95.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="101" t="s">
-        <v>149</v>
-      </c>
-      <c r="B33" s="99"/>
-      <c r="C33" s="99"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="100"/>
+      <c r="A33" s="107" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="D27:E27"/>
@@ -4866,45 +5159,6 @@
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
@@ -4924,7 +5178,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
@@ -4932,39 +5186,39 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="47.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" s="102" t="s">
-        <v>156</v>
+      <c r="A8" s="124" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="103"/>
+      <c r="A9" s="125"/>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" s="104"/>
+      <c r="A10" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2025zj/2025zj.xlsx
+++ b/2025zj/2025zj.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhong\Documents\GitHub\site\2025zj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E397179E-E6DA-451B-A2EB-3FA71E96DEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6449ADE0-F840-484F-86C0-D20C54DC6988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封面" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="279">
   <si>
     <t>申  报  书</t>
   </si>
@@ -737,10 +737,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>1993.1-1998.5</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>博士</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -770,10 +766,6 @@
   </si>
   <si>
     <t>高等数学，线性代数，概率统计的主讲（约100学生），发表论文3篇</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>1997.6-1997.12</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -787,10 +779,6 @@
   <si>
     <t>使用 Magic 将 DOS 版工业保险管理系统转换为 Windows 系统
 编写了200多个SQL存储过程。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>1998.4-1998.8</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -896,10 +884,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>某研究所</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>开发了用于图像配准的C++图像处理库。 
 基于TI DSP技术套件的机载图像压缩与传输 (C/C++版本)。 
 开发程序对装甲穿透实验进行统计建模。</t>
@@ -933,11 +917,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>本项目研究多种物理条件和假设条件下的水下声波建模，例如深度相关系数、分层海床、弹性海床或多孔弹性海床。针对各种条件和假设，我们寻求求解偏微分方程边界问题的算法，并进行数值模拟。我们还研究逆问题，即尝试利用边界数据求解深度相关系数。
-本研究发表了一系列论文。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>1995.7-1995.12</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -951,10 +930,6 @@
   </si>
   <si>
     <t>Lin Zhongyan</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>本项目研究径向对称和径向相关球域中的弹性方程组逆问题。我们尝试从边界力与位移之间的数据对应关系中恢复未知的拉梅系数。我们建立了问题的可解性和唯一性，并开发了数值模拟算法。</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -1188,7 +1163,122 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">大数据教学、学习与评估管理平台的功能TeaLeaMan加强和全球营销的三年工作计划
+    <r>
+      <t xml:space="preserve">在匿名评审过程中是否有需要回避的专家和单位，如果有，请详细列出：
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">       无</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>本人承诺以上信息真实、完整、有效，不存在违背科研诚信要求的行为，如有虚假信息愿意承担一切法律责任。入选后全职到岗工作，在国内连续工作不少于三年。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">
+                    申报人签字：                  日期：08/12/2025</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>启明计划</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>林中焰博士，不到16岁时以江西省修水县理科高考总分第一名考入四川大学数学系，后于湖南大学获硕士学位并留校任教。1993年获美国特拉华大学全额奖学金资助，于1997年、1998年分获计算机科学硕士及数学博士学位。早期研究聚焦数学物理方程可解性的数值模拟及其在海洋声学与弹性力学中的应用，成果发表于多篇学术论文，包括在著名的SIAM Appl. Math.的30页长文。
+博士毕业后，曾任职霍尼韦尔公司研发工程师。1999年重返学术界，全职任教于特拉华州立大学计算机与信息科学系。凭借杰出专业能力，于2004 获得终身教职（教学岗）。执教期间，系统讲授计算机及数学专业本硕课程25门，获美国高等教育协会教学认证。
+教学技术创新成就卓著：独立设计并开发了功能完备的基于Web的教学过程管理与质量评估系统（部署于古歌云上https://edqaa.com）。该系统采用全栈现代网络技术，源代码规模达12MB，已成功应用于特拉华州立大学中国校区的教学管理与质量保障。
+积极推动中美教育合作：近年来深度参与中国教育市场开拓，助力建立多个中美合作办学项目，并承担计算机专业核心教学任务。年授课量覆盖约600名学生注册（相当于国内原工作量的三倍），通过其系统高效管理，每课人均提交课业55项，年生成教学评估数据超200MB。其高效教学与基于大数据的质量管理体系连续三年通过严格评估，保障了合作项目的成功续签，累计为合作方创造经济效益约8000万元人民币，对应每年教学工作量贡献收益近300万美元。
+展望与宁波发展契合点：宁波作为新一线城市，高新智能产业领先，亟需提升高等教育质量以匹配城市发展新阶段。在生成式AI时代，教学资源易得，但教学质量保障面临新挑战（如受AI与网络娱乐冲击）。林博士希冀依托数十年教学经验与自主研发的成熟技术，整合进天宸启桦数字科技公司的强大平台，在宁波推广基于AI与大数据的智能化教学质量控制体系，助力宁波高等教育质量在短期内实现显著跃升，为城市创新发展提供强有力的人才与智力支撑。</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>天宸启桦公司成立于2019年，注册资金6000万元，拥有国内领先首创的XR+AI应用技术开发、动画内容设计制作和多媒体互动技术，主要研发利用物联网传感器实现基于AI算法的虚实实时交互的空间影像互动产品。公司旨在打造具有自主知识产权的高品质创新文化IP，拥有以XR技术为核心的全链条团队，能够提供从策划到研发、从技术到生产的一体化服务。公司力求将数字和产业融合，赋能行业实现数字产业化、产业数字化和数字化治理。通过虚拟现实、增强现实、人工智能、区块链、数字教育、数字文旅、数字孪生、游戏社交、商业消费等多种形式的线上线下体验产品，适用于文旅、学校、儿童友好、城市更新、乡村振兴、展览展 示、夜游消费等服务要求。曾承办和协办多起文旅推介和招商活动，荣获“创新先锋、新锐势力”双料大奖、小而美企业、国家高新技术企业等多项荣誉。为拓展产品类型与层次，公司将目光转向教育空间，以人体动态捕捉、实时手势感应、语音交互、数字光影展示、多屏融合等技术打造专属于儿童的沉浸式超媒体空间，赋能幼儿园、早教中心、社区等机构。技术是基底，内容才是核心。开发了安全、艺术、生态、科技、人文等九类主题1000多节课程的海量内容，真正打造了寓教于乐、虚实结合的儿童世界。目前，该项技术已应用到多家幼儿园和教学机构。2023年，广西首个省级超写实文旅数字推广大使数字人正式亮相，通过数字IP、数字导游、数字直播、数字展演等方式为游客提供向导服务，这也是公司在数字人领域的一大尝试。除了文旅产业，基于数据、算力和算法打造的数字人还可以运用在酒店、金融、医疗等场景，为消费者提供可靠、优质、便利的服务。公司正在谋划乡镇元宇宙项目，计划利用建筑、山体、树木、水系等载体，打造一个集灯光秀演、声光互动、虚实结合、亲子互动于一体的元宇宙场馆，包含科探馆、酒店、文旅接待中心等。</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>这段时间主要在学计算机专业课程，同时业写数学博士论文</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>1993年1月至1995年5月主要上数学专业博士课程博士资格考试。1997年6月论文大致完成后开始全职工作了，继续修改博士论文，1998年5月通过答辩，赶上8月一批的正式毕业。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>1993.1-1998.8</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>1997.6-1998.3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>1998.4-1999.8</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Army Research Lab</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>类似横向课题，主要是写程序</t>
+  </si>
+  <si>
+    <t>类似横向课题，主要是写程序</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件开发</t>
+  </si>
+  <si>
+    <t>软件开发</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>本项目研究多种物理条件和假设条件下的水下声波建模，例如深度相关系数、分层海床、弹性海床或多孔弹性海床。针对各种条件和假设，我们寻求求解偏微分方程边界问题的算法，并进行数值模拟。我们还研究逆问题，即尝试利用边界数据求解深度相关的介质物理参数。本研究发表了一系列论文。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>本项目研究径向对称和径向相关球域中的弹性方程组逆问题。我们尝试从边界力与位移之间的数据对应关系中求解未知的拉梅系数。我们建立了问题的可解性和唯一性，并开发了数值模拟算法。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁波工程学院信息科学专业的几百学生是中国校区的主要服务对象</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">大数据教学、学习与评估管理平台（TeaLeaMan）的功能加强和全球营销的三年工作计划
 一、背景与理念
 过去十年，数字教育飞速发展。多媒体内容、在线讲座和开放教育资源使得高质量的学习资料比以往任何时候都更容易获取。如今，生成式人工智能使学生能够即时完成作业、论文和习题集。虽然这些发展丰富了教学资源，但也暴露出一个关键的弱点：如果没有认真、结构化和频繁的评估，许多学生实际上并没有学习——无论课程准备得多么充分。
 在全球许多课堂中，缺乏一致且有数据支持的评估意味着学生可能被动地听课、一边看娱乐视频一边学习，或者完全不参与学习。等到期末考试来临时，为时已晚，无法扭转学习的损失，导致高挂失率和教育机会的浪费。
@@ -1223,69 +1313,8 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">在匿名评审过程中是否有需要回避的专家和单位，如果有，请详细列出：
-     </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">                         </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">       无</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t>本人承诺以上信息真实、完整、有效，不存在违背科研诚信要求的行为，如有虚假信息愿意承担一切法律责任。入选后全职到岗工作，在国内连续工作不少于三年。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">
-                    申报人签字：                  日期：08/12/2025</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>启明计划</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>林中焰博士，不到16岁时以江西省修水县理科高考总分第一名考入四川大学数学系，后于湖南大学获硕士学位并留校任教。1993年获美国特拉华大学全额奖学金资助，于1997年、1998年分获计算机科学硕士及数学博士学位。早期研究聚焦数学物理方程可解性的数值模拟及其在海洋声学与弹性力学中的应用，成果发表于多篇学术论文，包括在著名的SIAM Appl. Math.的30页长文。
-博士毕业后，曾任职霍尼韦尔公司研发工程师。1999年重返学术界，全职任教于特拉华州立大学计算机与信息科学系。凭借杰出专业能力，于2004 获得终身教职（教学岗）。执教期间，系统讲授计算机及数学专业本硕课程25门，获美国高等教育协会教学认证。
-教学技术创新成就卓著：独立设计并开发了功能完备的基于Web的教学过程管理与质量评估系统（部署于古歌云上https://edqaa.com）。该系统采用全栈现代网络技术，源代码规模达12MB，已成功应用于特拉华州立大学中国校区的教学管理与质量保障。
-积极推动中美教育合作：近年来深度参与中国教育市场开拓，助力建立多个中美合作办学项目，并承担计算机专业核心教学任务。年授课量覆盖约600名学生注册（相当于国内原工作量的三倍），通过其系统高效管理，每课人均提交课业55项，年生成教学评估数据超200MB。其高效教学与基于大数据的质量管理体系连续三年通过严格评估，保障了合作项目的成功续签，累计为合作方创造经济效益约8000万元人民币，对应每年教学工作量贡献收益近300万美元。
-展望与宁波发展契合点：宁波作为新一线城市，高新智能产业领先，亟需提升高等教育质量以匹配城市发展新阶段。在生成式AI时代，教学资源易得，但教学质量保障面临新挑战（如受AI与网络娱乐冲击）。林博士希冀依托数十年教学经验与自主研发的成熟技术，整合进天宸启桦数字科技公司的强大平台，在宁波推广基于AI与大数据的智能化教学质量控制体系，助力宁波高等教育质量在短期内实现显著跃升，为城市创新发展提供强有力的人才与智力支撑。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>天宸启桦公司成立于2019年，注册资金6000万元，拥有国内领先首创的XR+AI应用技术开发、动画内容设计制作和多媒体互动技术，主要研发利用物联网传感器实现基于AI算法的虚实实时交互的空间影像互动产品。公司旨在打造具有自主知识产权的高品质创新文化IP，拥有以XR技术为核心的全链条团队，能够提供从策划到研发、从技术到生产的一体化服务。公司力求将数字和产业融合，赋能行业实现数字产业化、产业数字化和数字化治理。通过虚拟现实、增强现实、人工智能、区块链、数字教育、数字文旅、数字孪生、游戏社交、商业消费等多种形式的线上线下体验产品，适用于文旅、学校、儿童友好、城市更新、乡村振兴、展览展 示、夜游消费等服务要求。曾承办和协办多起文旅推介和招商活动，荣获“创新先锋、新锐势力”双料大奖、小而美企业、国家高新技术企业等多项荣誉。为拓展产品类型与层次，公司将目光转向教育空间，以人体动态捕捉、实时手势感应、语音交互、数字光影展示、多屏融合等技术打造专属于儿童的沉浸式超媒体空间，赋能幼儿园、早教中心、社区等机构。技术是基底，内容才是核心。开发了安全、艺术、生态、科技、人文等九类主题1000多节课程的海量内容，真正打造了寓教于乐、虚实结合的儿童世界。目前，该项技术已应用到多家幼儿园和教学机构。2023年，广西首个省级超写实文旅数字推广大使数字人正式亮相，通过数字IP、数字导游、数字直播、数字展演等方式为游客提供向导服务，这也是公司在数字人领域的一大尝试。除了文旅产业，基于数据、算力和算法打造的数字人还可以运用在酒店、金融、医疗等场景，为消费者提供可靠、优质、便利的服务。公司正在谋划乡镇元宇宙项目，计划利用建筑、山体、树木、水系等载体，打造一个集灯光秀演、声光互动、虚实结合、亲子互动于一体的元宇宙场馆，包含科探馆、酒店、文旅接待中心等。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <t>这是硕士后的全职支薪工作，但业余修改博士论文</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1640,7 +1669,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1820,181 +1849,275 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top"/>
@@ -2008,55 +2131,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2066,49 +2140,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2118,74 +2151,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2574,194 +2539,194 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="54"/>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="A1" s="57"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="55"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="54"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="54"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
     </row>
     <row r="10" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="54"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="54"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="54"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="54"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="54"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
     </row>
     <row r="21" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="54"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="127" t="s">
-        <v>244</v>
+      <c r="C21" s="60" t="s">
+        <v>238</v>
       </c>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
@@ -2772,210 +2737,215 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="54"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
     </row>
     <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+      <c r="A23" s="57"/>
       <c r="B23" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="128" t="s">
-        <v>245</v>
-      </c>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
+      <c r="C23" s="62" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
     </row>
     <row r="24" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="57"/>
       <c r="B25" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="129" t="s">
-        <v>246</v>
-      </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
+      <c r="C25" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
     </row>
     <row r="26" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
     </row>
     <row r="27" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="54"/>
+      <c r="A27" s="57"/>
       <c r="B27" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="130" t="s">
-        <v>247</v>
-      </c>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
+      <c r="C27" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="54"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
+      <c r="A29" s="57"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="54"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
+      <c r="A30" s="57"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="54"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="54"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="54"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
+      <c r="A33" s="57"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="54"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="54"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="54"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="54"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="54"/>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="54"/>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="54"/>
-      <c r="B40" s="54"/>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="54"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="54"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="54"/>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:G5"/>
+    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="A8:G9"/>
+    <mergeCell ref="A11:G20"/>
+    <mergeCell ref="C25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="A21:A27"/>
@@ -2985,11 +2955,6 @@
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="B24:G24"/>
-    <mergeCell ref="A1:G5"/>
-    <mergeCell ref="A6:G7"/>
-    <mergeCell ref="A8:G9"/>
-    <mergeCell ref="A11:G20"/>
-    <mergeCell ref="C25:G25"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
@@ -3012,14 +2977,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
@@ -3033,13 +2998,13 @@
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="68" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="80" t="s">
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="75" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3047,42 +3012,42 @@
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="68" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="92"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="89"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="82"/>
+      <c r="C5" s="70"/>
       <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="F5" s="89"/>
+      <c r="F5" s="76"/>
     </row>
     <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="86" t="s">
+      <c r="C6" s="72"/>
+      <c r="D6" s="73" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="87"/>
+      <c r="E6" s="74"/>
       <c r="F6" s="34" t="s">
         <v>14</v>
       </c>
@@ -3091,43 +3056,43 @@
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="71" t="s">
         <v>152</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="86" t="s">
+      <c r="C7" s="77"/>
+      <c r="D7" s="73" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="87"/>
+      <c r="E7" s="74"/>
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="66"/>
+      <c r="C9" s="77"/>
       <c r="D9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="77">
+      <c r="E9" s="79">
         <v>546353345</v>
       </c>
-      <c r="F9" s="78"/>
+      <c r="F9" s="80"/>
     </row>
     <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -3136,285 +3101,255 @@
       <c r="B10" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="82"/>
+      <c r="C10" s="70"/>
       <c r="D10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="77">
+      <c r="E10" s="79">
         <v>3027728304</v>
       </c>
-      <c r="F10" s="78"/>
+      <c r="F10" s="80"/>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="83">
+      <c r="B11" s="82">
         <v>36373</v>
       </c>
-      <c r="C11" s="84"/>
+      <c r="C11" s="83"/>
       <c r="D11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="85" t="s">
+      <c r="E11" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="F11" s="78"/>
+      <c r="F11" s="80"/>
     </row>
     <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="71" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="79" t="s">
+      <c r="C12" s="72"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="F12" s="66"/>
+      <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="66"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="79" t="s">
+      <c r="C14" s="72"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="F14" s="66"/>
+      <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="80" t="s">
+      <c r="B15" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
     </row>
     <row r="16" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="79" t="s">
-        <v>248</v>
-      </c>
-      <c r="C16" s="66"/>
+      <c r="B16" s="71" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="77"/>
       <c r="D16" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="79" t="s">
-        <v>258</v>
-      </c>
-      <c r="F16" s="66"/>
+      <c r="E16" s="71" t="s">
+        <v>252</v>
+      </c>
+      <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="79" t="s">
-        <v>249</v>
-      </c>
-      <c r="C17" s="66"/>
+      <c r="B17" s="71" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="77"/>
       <c r="D17" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="E17" s="79" t="s">
-        <v>251</v>
-      </c>
-      <c r="F17" s="66"/>
+        <v>244</v>
+      </c>
+      <c r="E17" s="71" t="s">
+        <v>245</v>
+      </c>
+      <c r="F17" s="77"/>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="136" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="72"/>
+      <c r="B18" s="97" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="98"/>
       <c r="D18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="77">
+      <c r="E18" s="79">
         <v>17857322272</v>
       </c>
-      <c r="F18" s="78"/>
+      <c r="F18" s="80"/>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="71"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
+      <c r="A19" s="96"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="100"/>
       <c r="D19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="135" t="s">
-        <v>259</v>
-      </c>
-      <c r="F19" s="78"/>
+      <c r="E19" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="F19" s="80"/>
     </row>
     <row r="20" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="131" t="s">
-        <v>252</v>
-      </c>
-      <c r="C20" s="76"/>
+      <c r="B20" s="86" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="87"/>
       <c r="D20" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="131" t="s">
-        <v>253</v>
-      </c>
-      <c r="F20" s="76"/>
+      <c r="E20" s="86" t="s">
+        <v>247</v>
+      </c>
+      <c r="F20" s="87"/>
     </row>
     <row r="21" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="131" t="s">
-        <v>252</v>
-      </c>
-      <c r="C21" s="76"/>
+      <c r="B21" s="86" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" s="87"/>
       <c r="D21" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="131" t="s">
-        <v>268</v>
-      </c>
-      <c r="F21" s="76"/>
+      <c r="E21" s="86" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" s="87"/>
     </row>
     <row r="22" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="76"/>
+      <c r="C22" s="87"/>
       <c r="D22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="75"/>
-      <c r="F22" s="76"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="87"/>
     </row>
     <row r="23" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="132" t="s">
-        <v>255</v>
-      </c>
-      <c r="C23" s="76"/>
+      <c r="B23" s="102" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="87"/>
       <c r="D23" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="131" t="s">
-        <v>254</v>
-      </c>
-      <c r="F23" s="76"/>
+      <c r="E23" s="86" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" s="87"/>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="133" t="s">
-        <v>256</v>
-      </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
+      <c r="B24" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="79" t="s">
-        <v>257</v>
-      </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66"/>
+      <c r="B25" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="77"/>
     </row>
     <row r="26" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="134" t="s">
-        <v>269</v>
-      </c>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68"/>
+      <c r="B26" s="90" t="s">
+        <v>262</v>
+      </c>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="92"/>
     </row>
     <row r="27" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="137" t="s">
-        <v>270</v>
-      </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="70"/>
+      <c r="B27" s="93" t="s">
+        <v>263</v>
+      </c>
+      <c r="C27" s="94"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
@@ -3427,6 +3362,36 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F3:F5"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="1">
@@ -3444,7 +3409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3454,21 +3419,22 @@
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="7" width="19.25" customWidth="1"/>
     <col min="8" max="8" width="13.75" customWidth="1"/>
+    <col min="9" max="9" width="35.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -3477,7 +3443,7 @@
       <c r="F2" s="22"/>
       <c r="G2" s="31"/>
     </row>
-    <row r="3" spans="1:8" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
         <v>47</v>
       </c>
@@ -3488,7 +3454,7 @@
       <c r="F3" s="32"/>
       <c r="G3" s="33"/>
     </row>
-    <row r="4" spans="1:8" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
         <v>48</v>
       </c>
@@ -3499,7 +3465,7 @@
       <c r="F4" s="32"/>
       <c r="G4" s="33"/>
     </row>
-    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -3525,7 +3491,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="11"/>
@@ -3543,7 +3509,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -3567,7 +3533,7 @@
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -3591,7 +3557,7 @@
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>3</v>
       </c>
@@ -3614,13 +3580,16 @@
         <v>176</v>
       </c>
       <c r="H9" s="42" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="I9" s="140" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="40" t="s">
-        <v>177</v>
+        <v>266</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>173</v>
@@ -3632,16 +3601,19 @@
         <v>164</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G10" s="41" t="s">
         <v>176</v>
       </c>
       <c r="H10" s="42" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="I10" s="140" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="11"/>
@@ -3651,7 +3623,7 @@
       <c r="G11" s="11"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28" t="s">
         <v>61</v>
       </c>
@@ -3663,7 +3635,7 @@
       <c r="G13" s="33"/>
       <c r="H13" s="30"/>
     </row>
-    <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="28" t="s">
         <v>48</v>
       </c>
@@ -3675,7 +3647,7 @@
       <c r="G14" s="33"/>
       <c r="H14" s="30"/>
     </row>
-    <row r="15" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -3698,7 +3670,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="11"/>
@@ -3769,7 +3741,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.875" customWidth="1"/>
@@ -3779,23 +3751,23 @@
     <col min="7" max="7" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
     </row>
-    <row r="3" spans="1:7" s="27" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="27" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
         <v>63</v>
       </c>
@@ -3804,7 +3776,7 @@
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
     </row>
-    <row r="4" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
@@ -3827,7 +3799,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="11"/>
@@ -3842,31 +3814,31 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" s="40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6" s="41" t="s">
         <v>162</v>
       </c>
       <c r="D6" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="E6" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>182</v>
-      </c>
       <c r="G6" s="43" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>162</v>
@@ -3875,152 +3847,167 @@
         <v>168</v>
       </c>
       <c r="E7" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="42" t="s">
-        <v>185</v>
-      </c>
       <c r="G7" s="42" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="40" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>173</v>
       </c>
       <c r="D8" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>189</v>
-      </c>
       <c r="G8" s="42" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+      <c r="H8" s="140" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="40" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>173</v>
       </c>
       <c r="D9" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="114" x14ac:dyDescent="0.2">
+      <c r="B10" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="114" x14ac:dyDescent="0.2">
-      <c r="B10" s="45" t="s">
+      <c r="F10" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="F10" s="46" t="s">
+      <c r="G10" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="G10" s="49" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="57" x14ac:dyDescent="0.2">
-      <c r="B11" s="45" t="s">
-        <v>205</v>
+    </row>
+    <row r="11" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="51" t="s">
+        <v>210</v>
       </c>
       <c r="C11" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="44" t="s">
+      <c r="D11" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B12" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F11" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B12" s="44" t="s">
-        <v>210</v>
-      </c>
       <c r="C12" s="48" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>208</v>
+        <v>269</v>
+      </c>
+      <c r="E12" t="s">
+        <v>200</v>
       </c>
       <c r="F12" s="46" t="s">
         <v>209</v>
       </c>
       <c r="G12" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B13" s="51" t="s">
-        <v>211</v>
+        <v>197</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B13" s="44" t="s">
+        <v>207</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>212</v>
-      </c>
-      <c r="E13" t="s">
-        <v>203</v>
+        <v>204</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>205</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="G13" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="51" t="s">
-        <v>214</v>
+        <v>197</v>
+      </c>
+      <c r="H13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="57" x14ac:dyDescent="0.2">
+      <c r="B14" s="45" t="s">
+        <v>202</v>
       </c>
       <c r="C14" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="D14" s="46" t="s">
-        <v>215</v>
-      </c>
-      <c r="E14" t="s">
-        <v>203</v>
+      <c r="D14" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>205</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="G14" t="s">
-        <v>200</v>
+        <v>201</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="H14" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -4029,7 +4016,7 @@
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:C1048576 E12:F1048576 D1:E8 E10 D15:D1048576 F1:F10 D10:D13 G1:XFD1048576" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E8 D12:D1048576 A11:C1048576 A13:XFD13 E11:XFD1048576 F1:XFD10 D10:E10 A14:D14 A1:C10" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -4041,7 +4028,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -4051,18 +4038,18 @@
     <col min="7" max="7" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -4071,7 +4058,7 @@
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
     </row>
-    <row r="3" spans="1:7" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>49</v>
       </c>
@@ -4094,112 +4081,115 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25"/>
       <c r="B4" s="52" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="25"/>
       <c r="B5" s="52" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="G5" s="53" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="25"/>
       <c r="B6" s="52" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="25"/>
       <c r="B7" s="52" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="25"/>
       <c r="B8" s="52" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -4208,7 +4198,7 @@
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="25"/>
       <c r="B10" s="25"/>
       <c r="C10" s="25"/>
@@ -4217,7 +4207,7 @@
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
     </row>
-    <row r="11" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="25"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -4257,15 +4247,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="23"/>
@@ -4277,149 +4267,149 @@
       <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="97" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
+      <c r="B4" s="105" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="B5" s="107" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
     </row>
     <row r="6" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
     </row>
     <row r="7" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="96" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="B7" s="108" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
     </row>
     <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
     </row>
     <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="96" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
+      <c r="B10" s="108" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="106"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
     </row>
     <row r="11" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
     </row>
     <row r="12" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
     </row>
     <row r="13" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="106" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
     </row>
     <row r="14" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
     </row>
     <row r="15" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
     </row>
     <row r="16" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
     </row>
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
+      <c r="B17" s="104"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
     </row>
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
@@ -4509,13 +4499,13 @@
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="94"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="94"/>
-      <c r="E29" s="94"/>
+      <c r="B29" s="104"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
     </row>
     <row r="30" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
@@ -4599,16 +4589,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="B12:E12"/>
@@ -4616,6 +4596,16 @@
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
@@ -4632,16 +4622,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="22"/>
@@ -4654,52 +4644,52 @@
       <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
     </row>
     <row r="4" spans="1:8" ht="254.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="100" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
+      <c r="A4" s="110" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
     </row>
     <row r="5" spans="1:8" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="138" t="s">
-        <v>266</v>
-      </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
+      <c r="A5" s="112" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
     </row>
     <row r="6" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="139" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
+      <c r="A6" s="114" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4732,276 +4722,276 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="123"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
+      <c r="A2" s="116"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
     </row>
     <row r="4" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="71"/>
+      <c r="B4" s="96"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="71" t="s">
+      <c r="D4" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="71"/>
+      <c r="E4" s="96"/>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="96" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="96" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="96" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="71"/>
+      <c r="E5" s="96"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="71"/>
+      <c r="B6" s="96"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="114" t="s">
+      <c r="D6" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="115"/>
+      <c r="E6" s="118"/>
       <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="119" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="66"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="77"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="71"/>
+      <c r="B8" s="96"/>
       <c r="C8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="96" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="71"/>
+      <c r="E8" s="96"/>
       <c r="F8" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="71"/>
+      <c r="B9" s="96"/>
       <c r="C9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="71"/>
+      <c r="E9" s="96"/>
       <c r="F9" s="11" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="96" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="71"/>
+      <c r="B10" s="96"/>
       <c r="C10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="96" t="s">
         <v>111</v>
       </c>
-      <c r="E10" s="71"/>
+      <c r="E10" s="96"/>
       <c r="F10" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="119" t="s">
+      <c r="A11" s="121" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="120"/>
+      <c r="B11" s="122"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="119" t="s">
+      <c r="D11" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="120"/>
+      <c r="E11" s="122"/>
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="121" t="s">
+      <c r="A12" s="123" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="122"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="121" t="s">
+      <c r="D12" s="123" t="s">
         <v>115</v>
       </c>
-      <c r="E12" s="122"/>
+      <c r="E12" s="124"/>
       <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="119" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="71"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="113" t="s">
+      <c r="D13" s="119" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="71"/>
+      <c r="E13" s="96"/>
       <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="113" t="s">
+      <c r="A14" s="119" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="71"/>
+      <c r="B14" s="96"/>
       <c r="C14" s="15"/>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="71"/>
+      <c r="E14" s="96"/>
       <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="119" t="s">
         <v>120</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="63" t="s">
+      <c r="B15" s="96"/>
+      <c r="C15" s="89" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
     </row>
     <row r="16" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="114" t="s">
+      <c r="A16" s="117" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="115"/>
-      <c r="C16" s="116" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="125" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="118"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="127"/>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="104" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
       <c r="F18" s="17" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="18"/>
-      <c r="B19" s="108"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="110"/>
+      <c r="B19" s="128"/>
+      <c r="C19" s="129"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="130"/>
       <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="18"/>
-      <c r="B20" s="108"/>
-      <c r="C20" s="109"/>
-      <c r="D20" s="109"/>
-      <c r="E20" s="110"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="130"/>
       <c r="F20" s="18"/>
     </row>
     <row r="21" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="18"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="110"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="130"/>
       <c r="F21" s="18"/>
     </row>
     <row r="22" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="18"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="110"/>
+      <c r="B22" s="128"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="130"/>
       <c r="F22" s="18"/>
     </row>
     <row r="23" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="18"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="110"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="129"/>
+      <c r="E23" s="130"/>
       <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
@@ -5013,10 +5003,10 @@
       <c r="C25" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="111" t="s">
+      <c r="D25" s="131" t="s">
         <v>132</v>
       </c>
-      <c r="E25" s="112"/>
+      <c r="E25" s="132"/>
       <c r="F25" s="20" t="s">
         <v>133</v>
       </c>
@@ -5027,10 +5017,10 @@
         <v>134</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="75" t="s">
+      <c r="D26" s="101" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="76"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -5039,10 +5029,10 @@
         <v>134</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="101" t="s">
         <v>135</v>
       </c>
-      <c r="E27" s="76"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -5051,10 +5041,10 @@
         <v>134</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="75" t="s">
+      <c r="D28" s="101" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="76"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -5063,10 +5053,10 @@
         <v>134</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="75" t="s">
+      <c r="D29" s="101" t="s">
         <v>135</v>
       </c>
-      <c r="E29" s="76"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -5075,83 +5065,44 @@
         <v>134</v>
       </c>
       <c r="C30" s="4"/>
-      <c r="D30" s="75" t="s">
+      <c r="D30" s="101" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="76"/>
+      <c r="E30" s="87"/>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
     </row>
     <row r="32" spans="1:6" ht="86.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="104" t="s">
+      <c r="A32" s="133" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="105"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="106"/>
+      <c r="B32" s="134"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="134"/>
+      <c r="F32" s="135"/>
     </row>
     <row r="33" spans="1:6" ht="95.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="107" t="s">
+      <c r="A33" s="136" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="105"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="106"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="D27:E27"/>
@@ -5159,6 +5110,45 @@
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="1">
@@ -5210,15 +5200,15 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="137" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="125"/>
+      <c r="A9" s="138"/>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" s="126"/>
+      <c r="A10" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="1">
